--- a/inst/extdata/ExampleCont1.xlsx
+++ b/inst/extdata/ExampleCont1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proj\AquaSensR\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA24743-B44B-4CB0-B270-96146389F468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574D62B0-5309-4C32-ABCF-F835D267CFF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1890" yWindow="3120" windowWidth="26910" windowHeight="10770" xr2:uid="{F8A2AE6C-EDC3-4226-B9D4-2DE8A25DC7E8}"/>
+    <workbookView xWindow="-540" yWindow="252" windowWidth="21600" windowHeight="11232" xr2:uid="{F8A2AE6C-EDC3-4226-B9D4-2DE8A25DC7E8}"/>
   </bookViews>
   <sheets>
     <sheet name="YSI_SUD-DO_LoggerRaw" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Time</t>
-  </si>
-  <si>
-    <t>Water Temp_C</t>
   </si>
   <si>
     <t>DO_pctsat</t>
@@ -47,6 +44,9 @@
   </si>
   <si>
     <t>Salinity_ppt</t>
+  </si>
+  <si>
+    <t>Water_Temp_C</t>
   </si>
 </sst>
 </file>
@@ -910,20 +910,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE77DDD-C3F5-41D2-B839-75EBAE8AAC72}">
   <dimension ref="A1:I928"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -931,28 +931,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45518</v>
       </c>
@@ -981,7 +981,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45518</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45518</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>7.18</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45518</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>7.16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45518</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45518</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45518</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45518</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45518</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45518</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45518</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>7.11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45518</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45518</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45518</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>7.09</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45518</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45518</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45518</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45518</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45518</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45518</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>45518</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45518</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45518</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45518</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>45518</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>45518</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>45518</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>45518</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45518</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45518</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45518</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>45518</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>45518</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45518</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>45518</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>45518</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>45518</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>45518</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>45518</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45518</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45518</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45518</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45518</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45518</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45518</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45518</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45518</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45518</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45518</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45518</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45518</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45518</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45518</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45518</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45518</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45518</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45518</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45518</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45518</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45518</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45518</v>
       </c>
@@ -2721,7 +2721,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45518</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45518</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45518</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45518</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45518</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45518</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45518</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45518</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45518</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45518</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45518</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>45518</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>45518</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>45518</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>45518</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>45518</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>45518</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>45518</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>45518</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>45518</v>
       </c>
@@ -3301,7 +3301,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>45518</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>45518</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>45518</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>45518</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>45518</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>45518</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>45518</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>45518</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>45518</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45518</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45518</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>45518</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>45518</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>45518</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>45518</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>45518</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>45518</v>
       </c>
@@ -3794,7 +3794,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>45518</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>45518</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>45518</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>45518</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>45518</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>45518</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>45518</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>45518</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>45518</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>45518</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>45518</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>45518</v>
       </c>
@@ -4142,7 +4142,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>45518</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>45518</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>45518</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>45518</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>45518</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>45518</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>45518</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>45518</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>45518</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>45518</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>45518</v>
       </c>
@@ -4461,7 +4461,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>45518</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>45518</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>45518</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>45518</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>45518</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>45518</v>
       </c>
@@ -4635,7 +4635,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>45518</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>45518</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>45518</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>45518</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>45518</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>45518</v>
       </c>
@@ -4809,7 +4809,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>45518</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>45518</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>45518</v>
       </c>
@@ -4896,7 +4896,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>45518</v>
       </c>
@@ -4925,7 +4925,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>45518</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>45518</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>45518</v>
       </c>
@@ -5012,7 +5012,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>45518</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>45518</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>45518</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>45518</v>
       </c>
@@ -5128,7 +5128,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>45518</v>
       </c>
@@ -5157,7 +5157,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>45518</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>45518</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>45518</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>45518</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>45518</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>45518</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>45518</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>45518</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>45518</v>
       </c>
@@ -5418,7 +5418,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>45518</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>45518</v>
       </c>
@@ -5476,7 +5476,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>45518</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>45518</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>45518</v>
       </c>
@@ -5563,7 +5563,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>45518</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>45518</v>
       </c>
@@ -5621,7 +5621,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>45518</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>45518</v>
       </c>
@@ -5679,7 +5679,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>45518</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>45518</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>45518</v>
       </c>
@@ -5766,7 +5766,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>45518</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>45518</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>45518</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>45518</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>45518</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>45518</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>45518</v>
       </c>
@@ -5969,7 +5969,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>45518</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>45518</v>
       </c>
@@ -6027,7 +6027,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>45518</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>45518</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>45518</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>45518</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>45518</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>45518</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>45518</v>
       </c>
@@ -6230,7 +6230,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>45518</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>45518</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>45518</v>
       </c>
@@ -6317,7 +6317,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>45518</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>45518</v>
       </c>
@@ -6375,7 +6375,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>45518</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>45518</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>45518</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>45518</v>
       </c>
@@ -6491,7 +6491,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>45518</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>45518</v>
       </c>
@@ -6549,7 +6549,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>45518</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>45518</v>
       </c>
@@ -6607,7 +6607,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>45518</v>
       </c>
@@ -6636,7 +6636,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>45518</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>45518</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>45518</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>45518</v>
       </c>
@@ -6752,7 +6752,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>45518</v>
       </c>
@@ -6781,7 +6781,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>45518</v>
       </c>
@@ -6810,7 +6810,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>45518</v>
       </c>
@@ -6839,7 +6839,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>45518</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>45518</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>45518</v>
       </c>
@@ -6926,7 +6926,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>45518</v>
       </c>
@@ -6955,7 +6955,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>45518</v>
       </c>
@@ -6984,7 +6984,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>45518</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>45518</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>45518</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>45518</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>45518</v>
       </c>
@@ -7129,7 +7129,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>45518</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>45518</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>45518</v>
       </c>
@@ -7216,7 +7216,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>45518</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>45518</v>
       </c>
@@ -7274,7 +7274,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>45518</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>45518</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>45518</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>45518</v>
       </c>
@@ -7390,7 +7390,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>45518</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>45518</v>
       </c>
@@ -7448,7 +7448,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>45518</v>
       </c>
@@ -7477,7 +7477,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>45518</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>45518</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>45518</v>
       </c>
@@ -7564,7 +7564,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>45518</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>45518</v>
       </c>
@@ -7622,7 +7622,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>45518</v>
       </c>
@@ -7651,7 +7651,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>45518</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>45518</v>
       </c>
@@ -7709,7 +7709,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>45518</v>
       </c>
@@ -7738,7 +7738,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>45518</v>
       </c>
@@ -7767,7 +7767,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>45518</v>
       </c>
@@ -7796,7 +7796,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>45518</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>45518</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>45518</v>
       </c>
@@ -7883,7 +7883,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>45518</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>45518</v>
       </c>
@@ -7941,7 +7941,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>45518</v>
       </c>
@@ -7970,7 +7970,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>45518</v>
       </c>
@@ -7999,7 +7999,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>45518</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>45518</v>
       </c>
@@ -8057,7 +8057,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>45518</v>
       </c>
@@ -8086,7 +8086,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>45518</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>45518</v>
       </c>
@@ -8144,7 +8144,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>45518</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>45518</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>45518</v>
       </c>
@@ -8231,7 +8231,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>45518</v>
       </c>
@@ -8260,7 +8260,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>45518</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>45518</v>
       </c>
@@ -8318,7 +8318,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>45518</v>
       </c>
@@ -8347,7 +8347,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>45518</v>
       </c>
@@ -8376,7 +8376,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>45518</v>
       </c>
@@ -8405,7 +8405,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>45518</v>
       </c>
@@ -8434,7 +8434,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>45518</v>
       </c>
@@ -8463,7 +8463,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>45518</v>
       </c>
@@ -8492,7 +8492,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>45518</v>
       </c>
@@ -8521,7 +8521,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>45518</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>45518</v>
       </c>
@@ -8579,7 +8579,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>45518</v>
       </c>
@@ -8608,7 +8608,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>45518</v>
       </c>
@@ -8637,7 +8637,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>45518</v>
       </c>
@@ -8666,7 +8666,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>45518</v>
       </c>
@@ -8695,7 +8695,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>45518</v>
       </c>
@@ -8724,7 +8724,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>45518</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>45518</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>45518</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>45518</v>
       </c>
@@ -8840,7 +8840,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>45518</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>45518</v>
       </c>
@@ -8898,7 +8898,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>45518</v>
       </c>
@@ -8927,7 +8927,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>45518</v>
       </c>
@@ -8956,7 +8956,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>45518</v>
       </c>
@@ -8985,7 +8985,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>45518</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>45518</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>45518</v>
       </c>
@@ -9072,7 +9072,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>45518</v>
       </c>
@@ -9101,7 +9101,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>45518</v>
       </c>
@@ -9130,7 +9130,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>45518</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>45518</v>
       </c>
@@ -9188,7 +9188,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>45518</v>
       </c>
@@ -9217,7 +9217,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>45518</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>45518</v>
       </c>
@@ -9275,7 +9275,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>45518</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>45518</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>45518</v>
       </c>
@@ -9362,7 +9362,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>45518</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>45518</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>45518</v>
       </c>
@@ -9449,7 +9449,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>45518</v>
       </c>
@@ -9478,7 +9478,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>45518</v>
       </c>
@@ -9507,7 +9507,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>45518</v>
       </c>
@@ -9536,7 +9536,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>45518</v>
       </c>
@@ -9565,7 +9565,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>45518</v>
       </c>
@@ -9594,7 +9594,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>45518</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>45518</v>
       </c>
@@ -9652,7 +9652,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>45518</v>
       </c>
@@ -9681,7 +9681,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>45518</v>
       </c>
@@ -9710,7 +9710,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>45518</v>
       </c>
@@ -9739,7 +9739,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>45518</v>
       </c>
@@ -9768,7 +9768,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>45518</v>
       </c>
@@ -9797,7 +9797,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>45518</v>
       </c>
@@ -9826,7 +9826,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>45518</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>45518</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>45518</v>
       </c>
@@ -9913,7 +9913,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>45518</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>45518</v>
       </c>
@@ -9971,7 +9971,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>45518</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>45518</v>
       </c>
@@ -10029,7 +10029,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>45518</v>
       </c>
@@ -10058,7 +10058,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>45518</v>
       </c>
@@ -10087,7 +10087,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>45518</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>45518</v>
       </c>
@@ -10145,7 +10145,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>45518</v>
       </c>
@@ -10174,7 +10174,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>45518</v>
       </c>
@@ -10203,7 +10203,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>45518</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>45518</v>
       </c>
@@ -10261,7 +10261,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>45518</v>
       </c>
@@ -10290,7 +10290,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>45518</v>
       </c>
@@ -10319,7 +10319,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>45518</v>
       </c>
@@ -10348,7 +10348,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>45518</v>
       </c>
@@ -10377,7 +10377,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>45518</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>45518</v>
       </c>
@@ -10435,7 +10435,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>45518</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>45518</v>
       </c>
@@ -10493,7 +10493,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>45518</v>
       </c>
@@ -10522,7 +10522,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>45518</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>45518</v>
       </c>
@@ -10580,7 +10580,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>45518</v>
       </c>
@@ -10609,7 +10609,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>45518</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>45518</v>
       </c>
@@ -10667,7 +10667,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>45518</v>
       </c>
@@ -10696,7 +10696,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>45518</v>
       </c>
@@ -10725,7 +10725,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>45518</v>
       </c>
@@ -10754,7 +10754,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>45518</v>
       </c>
@@ -10783,7 +10783,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>45518</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>45518</v>
       </c>
@@ -10841,7 +10841,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>45518</v>
       </c>
@@ -10870,7 +10870,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>45518</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>45518</v>
       </c>
@@ -10928,7 +10928,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>45518</v>
       </c>
@@ -10957,7 +10957,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>45518</v>
       </c>
@@ -10986,7 +10986,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>45518</v>
       </c>
@@ -11015,7 +11015,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>45518</v>
       </c>
@@ -11044,7 +11044,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>45518</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>45518</v>
       </c>
@@ -11102,7 +11102,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>45518</v>
       </c>
@@ -11131,7 +11131,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>45518</v>
       </c>
@@ -11160,7 +11160,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>45518</v>
       </c>
@@ -11189,7 +11189,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>45518</v>
       </c>
@@ -11218,7 +11218,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>45518</v>
       </c>
@@ -11247,7 +11247,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>45518</v>
       </c>
@@ -11276,7 +11276,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>45518</v>
       </c>
@@ -11305,7 +11305,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>45518</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>45518</v>
       </c>
@@ -11363,7 +11363,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>45518</v>
       </c>
@@ -11392,7 +11392,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>45518</v>
       </c>
@@ -11421,7 +11421,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>45518</v>
       </c>
@@ -11450,7 +11450,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>45518</v>
       </c>
@@ -11479,7 +11479,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>45518</v>
       </c>
@@ -11508,7 +11508,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>45518</v>
       </c>
@@ -11537,7 +11537,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>45518</v>
       </c>
@@ -11566,7 +11566,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>45518</v>
       </c>
@@ -11595,7 +11595,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>45518</v>
       </c>
@@ -11624,7 +11624,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>45518</v>
       </c>
@@ -11653,7 +11653,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>45518</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>45518</v>
       </c>
@@ -11711,7 +11711,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>45518</v>
       </c>
@@ -11740,7 +11740,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>45518</v>
       </c>
@@ -11769,7 +11769,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>45518</v>
       </c>
@@ -11798,7 +11798,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>45518</v>
       </c>
@@ -11827,7 +11827,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>45518</v>
       </c>
@@ -11856,7 +11856,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>45518</v>
       </c>
@@ -11885,7 +11885,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>45518</v>
       </c>
@@ -11914,7 +11914,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>45518</v>
       </c>
@@ -11943,7 +11943,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>45518</v>
       </c>
@@ -11972,7 +11972,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>45518</v>
       </c>
@@ -12001,7 +12001,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>45518</v>
       </c>
@@ -12030,7 +12030,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>45518</v>
       </c>
@@ -12059,7 +12059,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>45518</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>45518</v>
       </c>
@@ -12117,7 +12117,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>45518</v>
       </c>
@@ -12146,7 +12146,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
         <v>45518</v>
       </c>
@@ -12175,7 +12175,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
         <v>45518</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>45518</v>
       </c>
@@ -12233,7 +12233,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
         <v>45518</v>
       </c>
@@ -12262,7 +12262,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
         <v>45518</v>
       </c>
@@ -12291,7 +12291,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
         <v>45518</v>
       </c>
@@ -12320,7 +12320,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
         <v>45518</v>
       </c>
@@ -12349,7 +12349,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A395" s="1">
         <v>45518</v>
       </c>
@@ -12378,7 +12378,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
         <v>45518</v>
       </c>
@@ -12407,7 +12407,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>45518</v>
       </c>
@@ -12436,7 +12436,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
         <v>45518</v>
       </c>
@@ -12465,7 +12465,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>45518</v>
       </c>
@@ -12494,7 +12494,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>45518</v>
       </c>
@@ -12523,7 +12523,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>45518</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>45518</v>
       </c>
@@ -12581,7 +12581,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>45518</v>
       </c>
@@ -12610,7 +12610,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>45518</v>
       </c>
@@ -12639,7 +12639,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>45518</v>
       </c>
@@ -12668,7 +12668,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>45518</v>
       </c>
@@ -12697,7 +12697,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
         <v>45518</v>
       </c>
@@ -12726,7 +12726,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
         <v>45518</v>
       </c>
@@ -12755,7 +12755,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>45518</v>
       </c>
@@ -12784,7 +12784,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>45518</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>45518</v>
       </c>
@@ -12842,7 +12842,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>45518</v>
       </c>
@@ -12871,7 +12871,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
         <v>45518</v>
       </c>
@@ -12900,7 +12900,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A414" s="1">
         <v>45518</v>
       </c>
@@ -12929,7 +12929,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A415" s="1">
         <v>45518</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
         <v>45518</v>
       </c>
@@ -12987,7 +12987,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417" s="1">
         <v>45518</v>
       </c>
@@ -13016,7 +13016,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>45518</v>
       </c>
@@ -13045,7 +13045,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>45518</v>
       </c>
@@ -13074,7 +13074,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A420" s="1">
         <v>45518</v>
       </c>
@@ -13103,7 +13103,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A421" s="1">
         <v>45518</v>
       </c>
@@ -13132,7 +13132,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
         <v>45518</v>
       </c>
@@ -13161,7 +13161,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
         <v>45518</v>
       </c>
@@ -13190,7 +13190,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A424" s="1">
         <v>45518</v>
       </c>
@@ -13219,7 +13219,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425" s="1">
         <v>45518</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>45518</v>
       </c>
@@ -13277,7 +13277,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
         <v>45518</v>
       </c>
@@ -13306,7 +13306,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428" s="1">
         <v>45518</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A429" s="1">
         <v>45518</v>
       </c>
@@ -13364,7 +13364,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
         <v>45518</v>
       </c>
@@ -13393,7 +13393,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
         <v>45518</v>
       </c>
@@ -13422,7 +13422,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432" s="1">
         <v>45518</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>45518</v>
       </c>
@@ -13480,7 +13480,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
         <v>45518</v>
       </c>
@@ -13509,7 +13509,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A435" s="1">
         <v>45518</v>
       </c>
@@ -13538,7 +13538,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A436" s="1">
         <v>45518</v>
       </c>
@@ -13567,7 +13567,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" s="1">
         <v>45518</v>
       </c>
@@ -13596,7 +13596,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>45518</v>
       </c>
@@ -13625,7 +13625,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A439" s="1">
         <v>45518</v>
       </c>
@@ -13654,7 +13654,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A440" s="1">
         <v>45518</v>
       </c>
@@ -13683,7 +13683,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A441" s="1">
         <v>45518</v>
       </c>
@@ -13712,7 +13712,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A442" s="1">
         <v>45518</v>
       </c>
@@ -13741,7 +13741,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A443" s="1">
         <v>45518</v>
       </c>
@@ -13770,7 +13770,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A444" s="1">
         <v>45518</v>
       </c>
@@ -13799,7 +13799,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A445" s="1">
         <v>45518</v>
       </c>
@@ -13828,7 +13828,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>45518</v>
       </c>
@@ -13857,7 +13857,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
         <v>45518</v>
       </c>
@@ -13886,7 +13886,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" s="1">
         <v>45518</v>
       </c>
@@ -13915,7 +13915,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" s="1">
         <v>45518</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" s="1">
         <v>45518</v>
       </c>
@@ -13973,7 +13973,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" s="1">
         <v>45518</v>
       </c>
@@ -14002,7 +14002,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" s="1">
         <v>45518</v>
       </c>
@@ -14031,7 +14031,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>45518</v>
       </c>
@@ -14060,7 +14060,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A454" s="1">
         <v>45518</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A455" s="1">
         <v>45518</v>
       </c>
@@ -14118,7 +14118,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>45518</v>
       </c>
@@ -14147,7 +14147,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A457" s="1">
         <v>45518</v>
       </c>
@@ -14176,7 +14176,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A458" s="1">
         <v>45518</v>
       </c>
@@ -14205,7 +14205,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>45518</v>
       </c>
@@ -14234,7 +14234,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>45518</v>
       </c>
@@ -14263,7 +14263,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>45518</v>
       </c>
@@ -14292,7 +14292,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>45518</v>
       </c>
@@ -14321,7 +14321,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>45518</v>
       </c>
@@ -14350,7 +14350,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>45518</v>
       </c>
@@ -14379,7 +14379,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>45518</v>
       </c>
@@ -14408,7 +14408,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>45518</v>
       </c>
@@ -14437,7 +14437,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>45518</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>45518</v>
       </c>
@@ -14495,7 +14495,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A469" s="1">
         <v>45518</v>
       </c>
@@ -14524,7 +14524,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A470" s="1">
         <v>45518</v>
       </c>
@@ -14553,7 +14553,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A471" s="1">
         <v>45518</v>
       </c>
@@ -14582,7 +14582,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>45518</v>
       </c>
@@ -14611,7 +14611,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A473" s="1">
         <v>45518</v>
       </c>
@@ -14640,7 +14640,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A474" s="1">
         <v>45518</v>
       </c>
@@ -14669,7 +14669,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A475" s="1">
         <v>45518</v>
       </c>
@@ -14698,7 +14698,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A476" s="1">
         <v>45518</v>
       </c>
@@ -14727,7 +14727,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A477" s="1">
         <v>45518</v>
       </c>
@@ -14756,7 +14756,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A478" s="1">
         <v>45518</v>
       </c>
@@ -14785,7 +14785,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A479" s="1">
         <v>45518</v>
       </c>
@@ -14814,7 +14814,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A480" s="1">
         <v>45518</v>
       </c>
@@ -14843,7 +14843,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A481" s="1">
         <v>45518</v>
       </c>
@@ -14872,7 +14872,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A482" s="1">
         <v>45518</v>
       </c>
@@ -14901,7 +14901,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A483" s="1">
         <v>45518</v>
       </c>
@@ -14930,7 +14930,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A484" s="1">
         <v>45518</v>
       </c>
@@ -14959,7 +14959,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>45518</v>
       </c>
@@ -14988,7 +14988,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>45518</v>
       </c>
@@ -15017,7 +15017,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A487" s="1">
         <v>45518</v>
       </c>
@@ -15046,7 +15046,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A488" s="1">
         <v>45518</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A489" s="1">
         <v>45518</v>
       </c>
@@ -15104,7 +15104,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>45518</v>
       </c>
@@ -15133,7 +15133,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A491" s="1">
         <v>45518</v>
       </c>
@@ -15162,7 +15162,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A492" s="1">
         <v>45518</v>
       </c>
@@ -15191,7 +15191,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A493" s="1">
         <v>45518</v>
       </c>
@@ -15220,7 +15220,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A494" s="1">
         <v>45518</v>
       </c>
@@ -15249,7 +15249,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A495" s="1">
         <v>45518</v>
       </c>
@@ -15278,7 +15278,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A496" s="1">
         <v>45518</v>
       </c>
@@ -15307,7 +15307,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A497" s="1">
         <v>45518</v>
       </c>
@@ -15336,7 +15336,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A498" s="1">
         <v>45518</v>
       </c>
@@ -15365,7 +15365,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A499" s="1">
         <v>45518</v>
       </c>
@@ -15394,7 +15394,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A500" s="1">
         <v>45518</v>
       </c>
@@ -15423,7 +15423,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A501" s="1">
         <v>45518</v>
       </c>
@@ -15452,7 +15452,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A502" s="1">
         <v>45518</v>
       </c>
@@ -15481,7 +15481,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>45518</v>
       </c>
@@ -15510,7 +15510,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>45518</v>
       </c>
@@ -15539,7 +15539,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A505" s="1">
         <v>45518</v>
       </c>
@@ -15568,7 +15568,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A506" s="1">
         <v>45518</v>
       </c>
@@ -15597,7 +15597,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A507" s="1">
         <v>45518</v>
       </c>
@@ -15626,7 +15626,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A508" s="1">
         <v>45518</v>
       </c>
@@ -15655,7 +15655,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A509" s="1">
         <v>45518</v>
       </c>
@@ -15684,7 +15684,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A510" s="1">
         <v>45518</v>
       </c>
@@ -15713,7 +15713,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A511" s="1">
         <v>45518</v>
       </c>
@@ -15742,7 +15742,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A512" s="1">
         <v>45518</v>
       </c>
@@ -15771,7 +15771,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A513" s="1">
         <v>45518</v>
       </c>
@@ -15800,7 +15800,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A514" s="1">
         <v>45518</v>
       </c>
@@ -15829,7 +15829,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A515" s="1">
         <v>45518</v>
       </c>
@@ -15858,7 +15858,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>45518</v>
       </c>
@@ -15887,7 +15887,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A517" s="1">
         <v>45518</v>
       </c>
@@ -15916,7 +15916,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A518" s="1">
         <v>45518</v>
       </c>
@@ -15945,7 +15945,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A519" s="1">
         <v>45518</v>
       </c>
@@ -15974,7 +15974,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A520" s="1">
         <v>45518</v>
       </c>
@@ -16003,7 +16003,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A521" s="1">
         <v>45518</v>
       </c>
@@ -16032,7 +16032,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A522" s="1">
         <v>45518</v>
       </c>
@@ -16061,7 +16061,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A523" s="1">
         <v>45518</v>
       </c>
@@ -16090,7 +16090,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A524" s="1">
         <v>45518</v>
       </c>
@@ -16119,7 +16119,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A525" s="1">
         <v>45518</v>
       </c>
@@ -16148,7 +16148,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A526" s="1">
         <v>45518</v>
       </c>
@@ -16177,7 +16177,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A527" s="1">
         <v>45518</v>
       </c>
@@ -16206,7 +16206,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A528" s="1">
         <v>45518</v>
       </c>
@@ -16235,7 +16235,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>45518</v>
       </c>
@@ -16264,7 +16264,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A530" s="1">
         <v>45518</v>
       </c>
@@ -16293,7 +16293,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A531" s="1">
         <v>45518</v>
       </c>
@@ -16322,7 +16322,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A532" s="1">
         <v>45518</v>
       </c>
@@ -16351,7 +16351,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A533" s="1">
         <v>45518</v>
       </c>
@@ -16380,7 +16380,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A534" s="1">
         <v>45518</v>
       </c>
@@ -16409,7 +16409,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A535" s="1">
         <v>45518</v>
       </c>
@@ -16438,7 +16438,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A536" s="1">
         <v>45518</v>
       </c>
@@ -16467,7 +16467,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A537" s="1">
         <v>45518</v>
       </c>
@@ -16496,7 +16496,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A538" s="1">
         <v>45518</v>
       </c>
@@ -16525,7 +16525,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A539" s="1">
         <v>45518</v>
       </c>
@@ -16554,7 +16554,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A540" s="1">
         <v>45518</v>
       </c>
@@ -16583,7 +16583,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A541" s="1">
         <v>45518</v>
       </c>
@@ -16612,7 +16612,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>45518</v>
       </c>
@@ -16641,7 +16641,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A543" s="1">
         <v>45518</v>
       </c>
@@ -16670,7 +16670,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>45518</v>
       </c>
@@ -16699,7 +16699,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>45518</v>
       </c>
@@ -16728,7 +16728,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>45518</v>
       </c>
@@ -16757,7 +16757,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>45518</v>
       </c>
@@ -16786,7 +16786,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>45518</v>
       </c>
@@ -16815,7 +16815,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>45518</v>
       </c>
@@ -16844,7 +16844,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>45518</v>
       </c>
@@ -16873,7 +16873,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A551" s="1">
         <v>45518</v>
       </c>
@@ -16902,7 +16902,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A552" s="1">
         <v>45518</v>
       </c>
@@ -16931,7 +16931,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>45518</v>
       </c>
@@ -16960,7 +16960,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A554" s="1">
         <v>45518</v>
       </c>
@@ -16989,7 +16989,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A555" s="1">
         <v>45518</v>
       </c>
@@ -17018,7 +17018,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A556" s="1">
         <v>45518</v>
       </c>
@@ -17047,7 +17047,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>45518</v>
       </c>
@@ -17076,7 +17076,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A558" s="1">
         <v>45518</v>
       </c>
@@ -17105,7 +17105,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A559" s="1">
         <v>45518</v>
       </c>
@@ -17134,7 +17134,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A560" s="1">
         <v>45518</v>
       </c>
@@ -17163,7 +17163,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A561" s="1">
         <v>45518</v>
       </c>
@@ -17192,7 +17192,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A562" s="1">
         <v>45518</v>
       </c>
@@ -17221,7 +17221,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A563" s="1">
         <v>45518</v>
       </c>
@@ -17250,7 +17250,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>45518</v>
       </c>
@@ -17279,7 +17279,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>45518</v>
       </c>
@@ -17308,7 +17308,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>45518</v>
       </c>
@@ -17337,7 +17337,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A567" s="1">
         <v>45518</v>
       </c>
@@ -17366,7 +17366,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A568" s="1">
         <v>45518</v>
       </c>
@@ -17395,7 +17395,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A569" s="1">
         <v>45518</v>
       </c>
@@ -17424,7 +17424,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A570" s="1">
         <v>45518</v>
       </c>
@@ -17453,7 +17453,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>45518</v>
       </c>
@@ -17482,7 +17482,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A572" s="1">
         <v>45518</v>
       </c>
@@ -17511,7 +17511,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A573" s="1">
         <v>45518</v>
       </c>
@@ -17540,7 +17540,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>45518</v>
       </c>
@@ -17569,7 +17569,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A575" s="1">
         <v>45518</v>
       </c>
@@ -17598,7 +17598,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A576" s="1">
         <v>45518</v>
       </c>
@@ -17627,7 +17627,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>45518</v>
       </c>
@@ -17656,7 +17656,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A578" s="1">
         <v>45518</v>
       </c>
@@ -17685,7 +17685,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A579" s="1">
         <v>45518</v>
       </c>
@@ -17714,7 +17714,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>45518</v>
       </c>
@@ -17743,7 +17743,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A581" s="1">
         <v>45518</v>
       </c>
@@ -17772,7 +17772,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A582" s="1">
         <v>45518</v>
       </c>
@@ -17801,7 +17801,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>45518</v>
       </c>
@@ -17830,7 +17830,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>45518</v>
       </c>
@@ -17859,7 +17859,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>45518</v>
       </c>
@@ -17888,7 +17888,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>45518</v>
       </c>
@@ -17917,7 +17917,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>45518</v>
       </c>
@@ -17946,7 +17946,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A588" s="1">
         <v>45518</v>
       </c>
@@ -17975,7 +17975,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A589" s="1">
         <v>45518</v>
       </c>
@@ -18004,7 +18004,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>45518</v>
       </c>
@@ -18033,7 +18033,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A591" s="1">
         <v>45518</v>
       </c>
@@ -18062,7 +18062,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A592" s="1">
         <v>45518</v>
       </c>
@@ -18091,7 +18091,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A593" s="1">
         <v>45518</v>
       </c>
@@ -18120,7 +18120,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A594" s="1">
         <v>45518</v>
       </c>
@@ -18149,7 +18149,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>45518</v>
       </c>
@@ -18178,7 +18178,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>45518</v>
       </c>
@@ -18207,7 +18207,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>45518</v>
       </c>
@@ -18236,7 +18236,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>45518</v>
       </c>
@@ -18265,7 +18265,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>45518</v>
       </c>
@@ -18294,7 +18294,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>45518</v>
       </c>
@@ -18323,7 +18323,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>45518</v>
       </c>
@@ -18352,7 +18352,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>45518</v>
       </c>
@@ -18381,7 +18381,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A603" s="1">
         <v>45518</v>
       </c>
@@ -18410,7 +18410,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A604" s="1">
         <v>45518</v>
       </c>
@@ -18439,7 +18439,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A605" s="1">
         <v>45518</v>
       </c>
@@ -18468,7 +18468,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A606" s="1">
         <v>45518</v>
       </c>
@@ -18497,7 +18497,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A607" s="1">
         <v>45518</v>
       </c>
@@ -18526,7 +18526,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A608" s="1">
         <v>45518</v>
       </c>
@@ -18555,7 +18555,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A609" s="1">
         <v>45518</v>
       </c>
@@ -18584,7 +18584,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A610" s="1">
         <v>45518</v>
       </c>
@@ -18613,7 +18613,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>45518</v>
       </c>
@@ -18642,7 +18642,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>45518</v>
       </c>
@@ -18671,7 +18671,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>45518</v>
       </c>
@@ -18700,7 +18700,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A614" s="1">
         <v>45518</v>
       </c>
@@ -18729,7 +18729,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A615" s="1">
         <v>45518</v>
       </c>
@@ -18758,7 +18758,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A616" s="1">
         <v>45518</v>
       </c>
@@ -18787,7 +18787,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A617" s="1">
         <v>45518</v>
       </c>
@@ -18816,7 +18816,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A618" s="1">
         <v>45518</v>
       </c>
@@ -18845,7 +18845,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A619" s="1">
         <v>45518</v>
       </c>
@@ -18874,7 +18874,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A620" s="1">
         <v>45518</v>
       </c>
@@ -18903,7 +18903,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A621" s="1">
         <v>45518</v>
       </c>
@@ -18932,7 +18932,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A622" s="1">
         <v>45518</v>
       </c>
@@ -18961,7 +18961,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>45518</v>
       </c>
@@ -18990,7 +18990,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>45518</v>
       </c>
@@ -19019,7 +19019,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>45518</v>
       </c>
@@ -19048,7 +19048,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>45518</v>
       </c>
@@ -19077,7 +19077,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>45518</v>
       </c>
@@ -19106,7 +19106,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>45518</v>
       </c>
@@ -19135,7 +19135,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>45518</v>
       </c>
@@ -19164,7 +19164,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>45518</v>
       </c>
@@ -19193,7 +19193,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A631" s="1">
         <v>45518</v>
       </c>
@@ -19222,7 +19222,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A632" s="1">
         <v>45518</v>
       </c>
@@ -19251,7 +19251,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A633" s="1">
         <v>45518</v>
       </c>
@@ -19280,7 +19280,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A634" s="1">
         <v>45518</v>
       </c>
@@ -19309,7 +19309,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A635" s="1">
         <v>45518</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A636" s="1">
         <v>45518</v>
       </c>
@@ -19367,7 +19367,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>45518</v>
       </c>
@@ -19396,7 +19396,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>45518</v>
       </c>
@@ -19425,7 +19425,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>45518</v>
       </c>
@@ -19454,7 +19454,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>45518</v>
       </c>
@@ -19483,7 +19483,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>45518</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>45518</v>
       </c>
@@ -19541,7 +19541,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>45518</v>
       </c>
@@ -19570,7 +19570,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A644" s="1">
         <v>45518</v>
       </c>
@@ -19599,7 +19599,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A645" s="1">
         <v>45518</v>
       </c>
@@ -19628,7 +19628,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A646" s="1">
         <v>45518</v>
       </c>
@@ -19657,7 +19657,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A647" s="1">
         <v>45518</v>
       </c>
@@ -19686,7 +19686,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A648" s="1">
         <v>45518</v>
       </c>
@@ -19715,7 +19715,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A649" s="1">
         <v>45518</v>
       </c>
@@ -19744,7 +19744,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A650" s="1">
         <v>45518</v>
       </c>
@@ -19773,7 +19773,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A651" s="1">
         <v>45518</v>
       </c>
@@ -19802,7 +19802,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A652" s="1">
         <v>45518</v>
       </c>
@@ -19831,7 +19831,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A653" s="1">
         <v>45518</v>
       </c>
@@ -19860,7 +19860,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A654" s="1">
         <v>45518</v>
       </c>
@@ -19889,7 +19889,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A655" s="1">
         <v>45518</v>
       </c>
@@ -19918,7 +19918,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A656" s="1">
         <v>45518</v>
       </c>
@@ -19947,7 +19947,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A657" s="1">
         <v>45518</v>
       </c>
@@ -19976,7 +19976,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A658" s="1">
         <v>45518</v>
       </c>
@@ -20005,7 +20005,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A659" s="1">
         <v>45518</v>
       </c>
@@ -20034,7 +20034,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A660" s="1">
         <v>45518</v>
       </c>
@@ -20063,7 +20063,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A661" s="1">
         <v>45518</v>
       </c>
@@ -20092,7 +20092,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A662" s="1">
         <v>45518</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A663" s="1">
         <v>45518</v>
       </c>
@@ -20150,7 +20150,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>45518</v>
       </c>
@@ -20179,7 +20179,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>45518</v>
       </c>
@@ -20208,7 +20208,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A666" s="1">
         <v>45518</v>
       </c>
@@ -20237,7 +20237,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A667" s="1">
         <v>45518</v>
       </c>
@@ -20266,7 +20266,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>45518</v>
       </c>
@@ -20295,7 +20295,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A669" s="1">
         <v>45518</v>
       </c>
@@ -20324,7 +20324,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A670" s="1">
         <v>45518</v>
       </c>
@@ -20353,7 +20353,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A671" s="1">
         <v>45518</v>
       </c>
@@ -20382,7 +20382,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A672" s="1">
         <v>45518</v>
       </c>
@@ -20411,7 +20411,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A673" s="1">
         <v>45518</v>
       </c>
@@ -20440,7 +20440,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A674" s="1">
         <v>45518</v>
       </c>
@@ -20469,7 +20469,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A675" s="1">
         <v>45518</v>
       </c>
@@ -20498,7 +20498,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A676" s="1">
         <v>45518</v>
       </c>
@@ -20527,7 +20527,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A677" s="1">
         <v>45518</v>
       </c>
@@ -20556,7 +20556,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>45518</v>
       </c>
@@ -20585,7 +20585,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A679" s="1">
         <v>45518</v>
       </c>
@@ -20614,7 +20614,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A680" s="1">
         <v>45518</v>
       </c>
@@ -20643,7 +20643,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A681" s="1">
         <v>45518</v>
       </c>
@@ -20672,7 +20672,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A682" s="1">
         <v>45518</v>
       </c>
@@ -20701,7 +20701,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A683" s="1">
         <v>45518</v>
       </c>
@@ -20730,7 +20730,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A684" s="1">
         <v>45518</v>
       </c>
@@ -20759,7 +20759,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A685" s="1">
         <v>45518</v>
       </c>
@@ -20788,7 +20788,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A686" s="1">
         <v>45518</v>
       </c>
@@ -20817,7 +20817,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A687" s="1">
         <v>45518</v>
       </c>
@@ -20846,7 +20846,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A688" s="1">
         <v>45518</v>
       </c>
@@ -20875,7 +20875,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A689" s="1">
         <v>45518</v>
       </c>
@@ -20904,7 +20904,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A690" s="1">
         <v>45518</v>
       </c>
@@ -20933,7 +20933,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A691" s="1">
         <v>45518</v>
       </c>
@@ -20962,7 +20962,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A692" s="1">
         <v>45518</v>
       </c>
@@ -20991,7 +20991,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A693" s="1">
         <v>45518</v>
       </c>
@@ -21020,7 +21020,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A694" s="1">
         <v>45518</v>
       </c>
@@ -21049,7 +21049,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A695" s="1">
         <v>45518</v>
       </c>
@@ -21078,7 +21078,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A696" s="1">
         <v>45518</v>
       </c>
@@ -21107,7 +21107,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A697" s="1">
         <v>45518</v>
       </c>
@@ -21136,7 +21136,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A698" s="1">
         <v>45518</v>
       </c>
@@ -21165,7 +21165,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A699" s="1">
         <v>45518</v>
       </c>
@@ -21194,7 +21194,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
         <v>45518</v>
       </c>
@@ -21223,7 +21223,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A701" s="1">
         <v>45518</v>
       </c>
@@ -21252,7 +21252,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A702" s="1">
         <v>45518</v>
       </c>
@@ -21281,7 +21281,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A703" s="1">
         <v>45518</v>
       </c>
@@ -21310,7 +21310,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A704" s="1">
         <v>45518</v>
       </c>
@@ -21339,7 +21339,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A705" s="1">
         <v>45518</v>
       </c>
@@ -21368,7 +21368,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A706" s="1">
         <v>45518</v>
       </c>
@@ -21397,7 +21397,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A707" s="1">
         <v>45518</v>
       </c>
@@ -21426,7 +21426,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A708" s="1">
         <v>45518</v>
       </c>
@@ -21455,7 +21455,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A709" s="1">
         <v>45518</v>
       </c>
@@ -21484,7 +21484,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A710" s="1">
         <v>45518</v>
       </c>
@@ -21513,7 +21513,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A711" s="1">
         <v>45518</v>
       </c>
@@ -21542,7 +21542,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A712" s="1">
         <v>45518</v>
       </c>
@@ -21571,7 +21571,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A713" s="1">
         <v>45518</v>
       </c>
@@ -21600,7 +21600,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A714" s="1">
         <v>45518</v>
       </c>
@@ -21629,7 +21629,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A715" s="1">
         <v>45518</v>
       </c>
@@ -21658,7 +21658,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A716" s="1">
         <v>45518</v>
       </c>
@@ -21687,7 +21687,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>45518</v>
       </c>
@@ -21716,7 +21716,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A718" s="1">
         <v>45518</v>
       </c>
@@ -21745,7 +21745,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A719" s="1">
         <v>45518</v>
       </c>
@@ -21774,7 +21774,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A720" s="1">
         <v>45518</v>
       </c>
@@ -21803,7 +21803,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A721" s="1">
         <v>45518</v>
       </c>
@@ -21832,7 +21832,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A722" s="1">
         <v>45518</v>
       </c>
@@ -21861,7 +21861,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A723" s="1">
         <v>45518</v>
       </c>
@@ -21890,7 +21890,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
         <v>45518</v>
       </c>
@@ -21919,7 +21919,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>45518</v>
       </c>
@@ -21948,7 +21948,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A726" s="1">
         <v>45518</v>
       </c>
@@ -21977,7 +21977,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A727" s="1">
         <v>45518</v>
       </c>
@@ -22006,7 +22006,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A728" s="1">
         <v>45518</v>
       </c>
@@ -22035,7 +22035,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A729" s="1">
         <v>45518</v>
       </c>
@@ -22064,7 +22064,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A730" s="1">
         <v>45518</v>
       </c>
@@ -22093,7 +22093,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A731" s="1">
         <v>45518</v>
       </c>
@@ -22122,7 +22122,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A732" s="1">
         <v>45518</v>
       </c>
@@ -22151,7 +22151,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A733" s="1">
         <v>45518</v>
       </c>
@@ -22180,7 +22180,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A734" s="1">
         <v>45518</v>
       </c>
@@ -22209,7 +22209,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>45518</v>
       </c>
@@ -22238,7 +22238,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>45518</v>
       </c>
@@ -22267,7 +22267,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>45518</v>
       </c>
@@ -22296,7 +22296,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A738" s="1">
         <v>45518</v>
       </c>
@@ -22325,7 +22325,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A739" s="1">
         <v>45518</v>
       </c>
@@ -22354,7 +22354,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A740" s="1">
         <v>45518</v>
       </c>
@@ -22383,7 +22383,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A741" s="1">
         <v>45518</v>
       </c>
@@ -22412,7 +22412,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A742" s="1">
         <v>45518</v>
       </c>
@@ -22441,7 +22441,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A743" s="1">
         <v>45518</v>
       </c>
@@ -22470,7 +22470,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A744" s="1">
         <v>45518</v>
       </c>
@@ -22499,7 +22499,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>45518</v>
       </c>
@@ -22528,7 +22528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A746" s="1">
         <v>45518</v>
       </c>
@@ -22557,7 +22557,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A747" s="1">
         <v>45518</v>
       </c>
@@ -22586,7 +22586,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A748" s="1">
         <v>45518</v>
       </c>
@@ -22615,7 +22615,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A749" s="1">
         <v>45518</v>
       </c>
@@ -22644,7 +22644,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A750" s="1">
         <v>45518</v>
       </c>
@@ -22673,7 +22673,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A751" s="1">
         <v>45518</v>
       </c>
@@ -22702,7 +22702,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A752" s="1">
         <v>45518</v>
       </c>
@@ -22731,7 +22731,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A753" s="1">
         <v>45518</v>
       </c>
@@ -22760,7 +22760,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A754" s="1">
         <v>45518</v>
       </c>
@@ -22789,7 +22789,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A755" s="1">
         <v>45518</v>
       </c>
@@ -22818,7 +22818,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
         <v>45518</v>
       </c>
@@ -22847,7 +22847,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A757" s="1">
         <v>45518</v>
       </c>
@@ -22876,7 +22876,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A758" s="1">
         <v>45518</v>
       </c>
@@ -22905,7 +22905,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A759" s="1">
         <v>45518</v>
       </c>
@@ -22934,7 +22934,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A760" s="1">
         <v>45518</v>
       </c>
@@ -22963,7 +22963,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A761" s="1">
         <v>45518</v>
       </c>
@@ -22992,7 +22992,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>45518</v>
       </c>
@@ -23021,7 +23021,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A763" s="1">
         <v>45518</v>
       </c>
@@ -23050,7 +23050,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A764" s="1">
         <v>45518</v>
       </c>
@@ -23079,7 +23079,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A765" s="1">
         <v>45518</v>
       </c>
@@ -23108,7 +23108,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A766" s="1">
         <v>45518</v>
       </c>
@@ -23137,7 +23137,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A767" s="1">
         <v>45518</v>
       </c>
@@ -23166,7 +23166,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A768" s="1">
         <v>45518</v>
       </c>
@@ -23195,7 +23195,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A769" s="1">
         <v>45518</v>
       </c>
@@ -23224,7 +23224,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A770" s="1">
         <v>45518</v>
       </c>
@@ -23253,7 +23253,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>45518</v>
       </c>
@@ -23282,7 +23282,7 @@
         <v>6.91</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A772" s="1">
         <v>45518</v>
       </c>
@@ -23311,7 +23311,7 @@
         <v>6.91</v>
       </c>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A773" s="1">
         <v>45518</v>
       </c>
@@ -23340,7 +23340,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A774" s="1">
         <v>45518</v>
       </c>
@@ -23369,7 +23369,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A775" s="1">
         <v>45518</v>
       </c>
@@ -23398,7 +23398,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A776" s="1">
         <v>45518</v>
       </c>
@@ -23427,7 +23427,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A777" s="1">
         <v>45518</v>
       </c>
@@ -23456,7 +23456,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A778" s="1">
         <v>45518</v>
       </c>
@@ -23485,7 +23485,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A779" s="1">
         <v>45518</v>
       </c>
@@ -23514,7 +23514,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A780" s="1">
         <v>45518</v>
       </c>
@@ -23543,7 +23543,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A781" s="1">
         <v>45518</v>
       </c>
@@ -23572,7 +23572,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>45518</v>
       </c>
@@ -23601,7 +23601,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>45518</v>
       </c>
@@ -23630,7 +23630,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>45518</v>
       </c>
@@ -23659,7 +23659,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A785" s="1">
         <v>45518</v>
       </c>
@@ -23688,7 +23688,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A786" s="1">
         <v>45518</v>
       </c>
@@ -23717,7 +23717,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A787" s="1">
         <v>45518</v>
       </c>
@@ -23746,7 +23746,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A788" s="1">
         <v>45518</v>
       </c>
@@ -23775,7 +23775,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A789" s="1">
         <v>45518</v>
       </c>
@@ -23804,7 +23804,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A790" s="1">
         <v>45518</v>
       </c>
@@ -23833,7 +23833,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A791" s="1">
         <v>45518</v>
       </c>
@@ -23862,7 +23862,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A792" s="1">
         <v>45518</v>
       </c>
@@ -23891,7 +23891,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A793" s="1">
         <v>45518</v>
       </c>
@@ -23920,7 +23920,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A794" s="1">
         <v>45518</v>
       </c>
@@ -23949,7 +23949,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A795" s="1">
         <v>45518</v>
       </c>
@@ -23978,7 +23978,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A796" s="1">
         <v>45518</v>
       </c>
@@ -24007,7 +24007,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A797" s="1">
         <v>45518</v>
       </c>
@@ -24036,7 +24036,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A798" s="1">
         <v>45518</v>
       </c>
@@ -24065,7 +24065,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A799" s="1">
         <v>45518</v>
       </c>
@@ -24094,7 +24094,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A800" s="1">
         <v>45518</v>
       </c>
@@ -24123,7 +24123,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A801" s="1">
         <v>45518</v>
       </c>
@@ -24152,7 +24152,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A802" s="1">
         <v>45518</v>
       </c>
@@ -24181,7 +24181,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A803" s="1">
         <v>45518</v>
       </c>
@@ -24210,7 +24210,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A804" s="1">
         <v>45518</v>
       </c>
@@ -24239,7 +24239,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A805" s="1">
         <v>45518</v>
       </c>
@@ -24268,7 +24268,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A806" s="1">
         <v>45518</v>
       </c>
@@ -24297,7 +24297,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A807" s="1">
         <v>45518</v>
       </c>
@@ -24326,7 +24326,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A808" s="1">
         <v>45518</v>
       </c>
@@ -24355,7 +24355,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A809" s="1">
         <v>45518</v>
       </c>
@@ -24384,7 +24384,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A810" s="1">
         <v>45518</v>
       </c>
@@ -24413,7 +24413,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A811" s="1">
         <v>45518</v>
       </c>
@@ -24442,7 +24442,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A812" s="1">
         <v>45518</v>
       </c>
@@ -24471,7 +24471,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A813" s="1">
         <v>45518</v>
       </c>
@@ -24500,7 +24500,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A814" s="1">
         <v>45518</v>
       </c>
@@ -24529,7 +24529,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A815" s="1">
         <v>45518</v>
       </c>
@@ -24558,7 +24558,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A816" s="1">
         <v>45518</v>
       </c>
@@ -24587,7 +24587,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A817" s="1">
         <v>45518</v>
       </c>
@@ -24616,7 +24616,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A818" s="1">
         <v>45518</v>
       </c>
@@ -24645,7 +24645,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A819" s="1">
         <v>45518</v>
       </c>
@@ -24674,7 +24674,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A820" s="1">
         <v>45518</v>
       </c>
@@ -24703,7 +24703,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A821" s="1">
         <v>45518</v>
       </c>
@@ -24732,7 +24732,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A822" s="1">
         <v>45518</v>
       </c>
@@ -24761,7 +24761,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A823" s="1">
         <v>45518</v>
       </c>
@@ -24790,7 +24790,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A824" s="1">
         <v>45518</v>
       </c>
@@ -24819,7 +24819,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A825" s="1">
         <v>45518</v>
       </c>
@@ -24848,7 +24848,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A826" s="1">
         <v>45518</v>
       </c>
@@ -24877,7 +24877,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A827" s="1">
         <v>45518</v>
       </c>
@@ -24906,7 +24906,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A828" s="1">
         <v>45518</v>
       </c>
@@ -24935,7 +24935,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A829" s="1">
         <v>45518</v>
       </c>
@@ -24964,7 +24964,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A830" s="1">
         <v>45518</v>
       </c>
@@ -24993,7 +24993,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A831" s="1">
         <v>45518</v>
       </c>
@@ -25022,7 +25022,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A832" s="1">
         <v>45518</v>
       </c>
@@ -25051,7 +25051,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A833" s="1">
         <v>45518</v>
       </c>
@@ -25080,7 +25080,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A834" s="1">
         <v>45518</v>
       </c>
@@ -25109,7 +25109,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A835" s="1">
         <v>45518</v>
       </c>
@@ -25138,7 +25138,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A836" s="1">
         <v>45518</v>
       </c>
@@ -25167,7 +25167,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A837" s="1">
         <v>45518</v>
       </c>
@@ -25196,7 +25196,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A838" s="1">
         <v>45518</v>
       </c>
@@ -25225,7 +25225,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A839" s="1">
         <v>45518</v>
       </c>
@@ -25254,7 +25254,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A840" s="1">
         <v>45518</v>
       </c>
@@ -25283,7 +25283,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A841" s="1">
         <v>45518</v>
       </c>
@@ -25312,7 +25312,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A842" s="1">
         <v>45518</v>
       </c>
@@ -25341,7 +25341,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A843" s="1">
         <v>45518</v>
       </c>
@@ -25370,7 +25370,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A844" s="1">
         <v>45518</v>
       </c>
@@ -25399,7 +25399,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A845" s="1">
         <v>45518</v>
       </c>
@@ -25428,7 +25428,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A846" s="1">
         <v>45518</v>
       </c>
@@ -25457,7 +25457,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A847" s="1">
         <v>45518</v>
       </c>
@@ -25486,7 +25486,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A848" s="1">
         <v>45518</v>
       </c>
@@ -25515,7 +25515,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A849" s="1">
         <v>45518</v>
       </c>
@@ -25544,7 +25544,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A850" s="1">
         <v>45518</v>
       </c>
@@ -25573,7 +25573,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A851" s="1">
         <v>45518</v>
       </c>
@@ -25602,7 +25602,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A852" s="1">
         <v>45518</v>
       </c>
@@ -25631,7 +25631,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A853" s="1">
         <v>45518</v>
       </c>
@@ -25660,7 +25660,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A854" s="1">
         <v>45518</v>
       </c>
@@ -25689,7 +25689,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A855" s="1">
         <v>45518</v>
       </c>
@@ -25718,7 +25718,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A856" s="1">
         <v>45518</v>
       </c>
@@ -25747,7 +25747,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A857" s="1">
         <v>45518</v>
       </c>
@@ -25776,7 +25776,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A858" s="1">
         <v>45518</v>
       </c>
@@ -25805,7 +25805,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A859" s="1">
         <v>45518</v>
       </c>
@@ -25834,7 +25834,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A860" s="1">
         <v>45518</v>
       </c>
@@ -25863,7 +25863,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A861" s="1">
         <v>45518</v>
       </c>
@@ -25892,7 +25892,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A862" s="1">
         <v>45518</v>
       </c>
@@ -25921,7 +25921,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A863" s="1">
         <v>45518</v>
       </c>
@@ -25950,7 +25950,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A864" s="1">
         <v>45518</v>
       </c>
@@ -25979,7 +25979,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A865" s="1">
         <v>45518</v>
       </c>
@@ -26008,7 +26008,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A866" s="1">
         <v>45518</v>
       </c>
@@ -26037,7 +26037,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A867" s="1">
         <v>45518</v>
       </c>
@@ -26066,7 +26066,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A868" s="1">
         <v>45518</v>
       </c>
@@ -26095,7 +26095,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A869" s="1">
         <v>45518</v>
       </c>
@@ -26124,7 +26124,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A870" s="1">
         <v>45518</v>
       </c>
@@ -26153,7 +26153,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A871" s="1">
         <v>45518</v>
       </c>
@@ -26182,7 +26182,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A872" s="1">
         <v>45518</v>
       </c>
@@ -26211,7 +26211,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A873" s="1">
         <v>45518</v>
       </c>
@@ -26240,7 +26240,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A874" s="1">
         <v>45518</v>
       </c>
@@ -26269,7 +26269,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A875" s="1">
         <v>45518</v>
       </c>
@@ -26298,7 +26298,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A876" s="1">
         <v>45518</v>
       </c>
@@ -26327,7 +26327,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A877" s="1">
         <v>45518</v>
       </c>
@@ -26356,7 +26356,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A878" s="1">
         <v>45518</v>
       </c>
@@ -26385,7 +26385,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A879" s="1">
         <v>45518</v>
       </c>
@@ -26414,7 +26414,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A880" s="1">
         <v>45518</v>
       </c>
@@ -26443,7 +26443,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A881" s="1">
         <v>45518</v>
       </c>
@@ -26472,7 +26472,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A882" s="1">
         <v>45518</v>
       </c>
@@ -26501,7 +26501,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A883" s="1">
         <v>45518</v>
       </c>
@@ -26530,7 +26530,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A884" s="1">
         <v>45518</v>
       </c>
@@ -26559,7 +26559,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A885" s="1">
         <v>45518</v>
       </c>
@@ -26588,7 +26588,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A886" s="1">
         <v>45518</v>
       </c>
@@ -26617,7 +26617,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A887" s="1">
         <v>45518</v>
       </c>
@@ -26646,7 +26646,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A888" s="1">
         <v>45518</v>
       </c>
@@ -26675,7 +26675,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A889" s="1">
         <v>45518</v>
       </c>
@@ -26704,7 +26704,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A890" s="1">
         <v>45518</v>
       </c>
@@ -26733,7 +26733,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A891" s="1">
         <v>45518</v>
       </c>
@@ -26762,7 +26762,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A892" s="1">
         <v>45518</v>
       </c>
@@ -26791,7 +26791,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A893" s="1">
         <v>45518</v>
       </c>
@@ -26820,7 +26820,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A894" s="1">
         <v>45518</v>
       </c>
@@ -26849,7 +26849,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A895" s="1">
         <v>45518</v>
       </c>
@@ -26878,7 +26878,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A896" s="1">
         <v>45518</v>
       </c>
@@ -26907,7 +26907,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A897" s="1">
         <v>45518</v>
       </c>
@@ -26936,7 +26936,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A898" s="1">
         <v>45518</v>
       </c>
@@ -26965,7 +26965,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A899" s="1">
         <v>45518</v>
       </c>
@@ -26994,7 +26994,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A900" s="1">
         <v>45518</v>
       </c>
@@ -27023,7 +27023,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A901" s="1">
         <v>45518</v>
       </c>
@@ -27052,7 +27052,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A902" s="1">
         <v>45518</v>
       </c>
@@ -27081,7 +27081,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A903" s="1">
         <v>45518</v>
       </c>
@@ -27110,7 +27110,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A904" s="1">
         <v>45518</v>
       </c>
@@ -27139,7 +27139,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A905" s="1">
         <v>45518</v>
       </c>
@@ -27168,7 +27168,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A906" s="1">
         <v>45518</v>
       </c>
@@ -27197,7 +27197,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A907" s="1">
         <v>45518</v>
       </c>
@@ -27226,7 +27226,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A908" s="1">
         <v>45518</v>
       </c>
@@ -27255,7 +27255,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A909" s="1">
         <v>45518</v>
       </c>
@@ -27284,7 +27284,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A910" s="1">
         <v>45518</v>
       </c>
@@ -27313,7 +27313,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A911" s="1">
         <v>45518</v>
       </c>
@@ -27342,7 +27342,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A912" s="1">
         <v>45518</v>
       </c>
@@ -27371,7 +27371,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A913" s="1">
         <v>45518</v>
       </c>
@@ -27400,7 +27400,7 @@
         <v>6.91</v>
       </c>
     </row>
-    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A914" s="1">
         <v>45518</v>
       </c>
@@ -27429,7 +27429,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A915" s="1">
         <v>45518</v>
       </c>
@@ -27458,7 +27458,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A916" s="1">
         <v>45518</v>
       </c>
@@ -27487,7 +27487,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A917" s="1">
         <v>45518</v>
       </c>
@@ -27516,7 +27516,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="918" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A918" s="1">
         <v>45518</v>
       </c>
@@ -27545,7 +27545,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A919" s="1">
         <v>45518</v>
       </c>
@@ -27574,7 +27574,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="920" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A920" s="1">
         <v>45518</v>
       </c>
@@ -27603,7 +27603,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A921" s="1">
         <v>45518</v>
       </c>
@@ -27632,7 +27632,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A922" s="1">
         <v>45518</v>
       </c>
@@ -27661,7 +27661,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A923" s="1">
         <v>45518</v>
       </c>
@@ -27690,7 +27690,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A924" s="1">
         <v>45518</v>
       </c>
@@ -27719,7 +27719,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A925" s="1">
         <v>45518</v>
       </c>
@@ -27748,7 +27748,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A926" s="1">
         <v>45518</v>
       </c>
@@ -27777,7 +27777,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A927" s="1">
         <v>45518</v>
       </c>
@@ -27806,7 +27806,7 @@
         <v>7.16</v>
       </c>
     </row>
-    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A928" s="1">
         <v>45518</v>
       </c>
